--- a/SGC-CKN/Excel/f51fae94-b61d-4049-b538-df269cc1ebda_Khách_sạn_Grand_Hyatt_TN_B3_B2_88_D1200_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/f51fae94-b61d-4049-b538-df269cc1ebda_Khách_sạn_Grand_Hyatt_TN_B3_B2_88_D1200_19-03-2026.xlsx
@@ -1572,7 +1572,7 @@
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>11</v>

--- a/SGC-CKN/Excel/f51fae94-b61d-4049-b538-df269cc1ebda_Khách_sạn_Grand_Hyatt_TN_B3_B2_88_D1200_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/f51fae94-b61d-4049-b538-df269cc1ebda_Khách_sạn_Grand_Hyatt_TN_B3_B2_88_D1200_19-03-2026.xlsx
@@ -441,6 +441,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
@@ -452,11 +457,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -597,35 +597,35 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1584,7 +1584,7 @@
         <v>43</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F21" s="9">
         <v>-16.09</v>
@@ -1593,13 +1593,13 @@
         <v>-18.1</v>
       </c>
       <c r="H21" s="9">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="I21" s="9">
         <v>2.01</v>
       </c>
-      <c r="J21" s="8">
-        <v>15.08</v>
+      <c r="J21" s="12">
+        <v>4.02</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>30</v>
@@ -1641,632 +1641,632 @@
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="13" t="s">
+      <c r="B23" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="13">
         <v>-20.12</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="13">
         <v>-22.1</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="13">
         <v>0.22</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="13">
         <v>1.98</v>
       </c>
       <c r="J23" s="8">
         <v>9.14</v>
       </c>
-      <c r="K23" s="13" t="s">
+      <c r="K23" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="16">
         <v>-22.1</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="16">
         <v>-24.12</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="16">
         <v>0.2</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="16">
         <v>2.02</v>
       </c>
       <c r="J24" s="8">
         <v>10.1</v>
       </c>
-      <c r="K24" s="16" t="s">
+      <c r="K24" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="B25" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="16">
         <v>-24.12</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="16">
         <v>-26.1</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="16">
         <v>0.13</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="16">
         <v>1.98</v>
       </c>
       <c r="J25" s="8">
         <v>14.85</v>
       </c>
-      <c r="K25" s="16" t="s">
+      <c r="K25" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="19" t="s">
+      <c r="B26" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="19">
         <v>-26.1</v>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="19">
         <v>-28.11</v>
       </c>
-      <c r="H26" s="18">
+      <c r="H26" s="19">
         <v>0.33</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="19">
         <v>2.01</v>
       </c>
       <c r="J26" s="8">
         <v>6.03</v>
       </c>
-      <c r="K26" s="19" t="s">
+      <c r="K26" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="19" t="s">
+      <c r="B27" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="19">
         <v>-28.11</v>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="19">
         <v>-30.13</v>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="19">
         <v>0.5</v>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="19">
         <v>2.02</v>
       </c>
-      <c r="J27" s="21">
+      <c r="J27" s="12">
         <v>4.04</v>
       </c>
-      <c r="K27" s="19" t="s">
+      <c r="K27" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="19" t="s">
+      <c r="B28" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="19">
         <v>-30.13</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="19">
         <v>-32.1</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="19">
         <v>0.33</v>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="19">
         <v>1.97</v>
       </c>
       <c r="J28" s="8">
         <v>5.91</v>
       </c>
-      <c r="K28" s="19" t="s">
+      <c r="K28" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="19" t="s">
+      <c r="B29" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="19">
         <v>-32.1</v>
       </c>
-      <c r="G29" s="18">
+      <c r="G29" s="19">
         <v>-34.12</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="19">
         <v>0.42</v>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="19">
         <v>2.02</v>
       </c>
-      <c r="J29" s="21">
+      <c r="J29" s="12">
         <v>4.85</v>
       </c>
-      <c r="K29" s="19" t="s">
+      <c r="K29" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="19" t="s">
+      <c r="B30" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="19">
         <v>-34.12</v>
       </c>
-      <c r="G30" s="18">
-        <v>-36.11</v>
-      </c>
-      <c r="H30" s="18">
+      <c r="G30" s="19">
+        <v>-36.10999999999999</v>
+      </c>
+      <c r="H30" s="19">
         <v>0.37</v>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="19">
         <v>1.99</v>
       </c>
       <c r="J30" s="8">
         <v>5.43</v>
       </c>
-      <c r="K30" s="19" t="s">
+      <c r="K30" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="19" t="s">
+      <c r="B31" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="18">
-        <v>-36.11</v>
-      </c>
-      <c r="G31" s="18">
-        <v>-38.13</v>
-      </c>
-      <c r="H31" s="18">
+      <c r="F31" s="19">
+        <v>-36.10999999999999</v>
+      </c>
+      <c r="G31" s="19">
+        <v>-38.12999999999999</v>
+      </c>
+      <c r="H31" s="19">
         <v>0.3</v>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="19">
         <v>2.02</v>
       </c>
       <c r="J31" s="8">
         <v>6.73</v>
       </c>
-      <c r="K31" s="19" t="s">
+      <c r="K31" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="19" t="s">
+      <c r="B32" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="F32" s="18">
-        <v>-38.13</v>
-      </c>
-      <c r="G32" s="18">
-        <v>-40.09</v>
-      </c>
-      <c r="H32" s="18">
+      <c r="F32" s="19">
+        <v>-38.12999999999999</v>
+      </c>
+      <c r="G32" s="19">
+        <v>-40.08999999999999</v>
+      </c>
+      <c r="H32" s="19">
         <v>0.33</v>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="19">
         <v>1.96</v>
       </c>
       <c r="J32" s="8">
         <v>5.88</v>
       </c>
-      <c r="K32" s="19" t="s">
+      <c r="K32" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="19" t="s">
+      <c r="B33" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="18">
-        <v>-40.09</v>
-      </c>
-      <c r="G33" s="18">
-        <v>-42.1</v>
-      </c>
-      <c r="H33" s="18">
+      <c r="F33" s="19">
+        <v>-40.08999999999999</v>
+      </c>
+      <c r="G33" s="19">
+        <v>-42.09999999999999</v>
+      </c>
+      <c r="H33" s="19">
         <v>0.17</v>
       </c>
-      <c r="I33" s="18">
+      <c r="I33" s="19">
         <v>2.01</v>
       </c>
       <c r="J33" s="8">
         <v>12.06</v>
       </c>
-      <c r="K33" s="19" t="s">
+      <c r="K33" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="19" t="s">
+      <c r="B34" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="18">
-        <v>-42.1</v>
-      </c>
-      <c r="G34" s="18">
-        <v>-44.12</v>
-      </c>
-      <c r="H34" s="18">
+      <c r="F34" s="19">
+        <v>-42.09999999999999</v>
+      </c>
+      <c r="G34" s="19">
+        <v>-44.11999999999998</v>
+      </c>
+      <c r="H34" s="19">
         <v>0.13</v>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="19">
         <v>2.02</v>
       </c>
       <c r="J34" s="8">
         <v>15.15</v>
       </c>
-      <c r="K34" s="19" t="s">
+      <c r="K34" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="19" t="s">
+      <c r="B35" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="F35" s="18">
-        <v>-44.12</v>
-      </c>
-      <c r="G35" s="18">
-        <v>-46.1</v>
-      </c>
-      <c r="H35" s="18">
+      <c r="F35" s="19">
+        <v>-44.11999999999998</v>
+      </c>
+      <c r="G35" s="19">
+        <v>-46.09999999999999</v>
+      </c>
+      <c r="H35" s="19">
         <v>0.18</v>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="19">
         <v>1.98</v>
       </c>
       <c r="J35" s="8">
         <v>10.8</v>
       </c>
-      <c r="K35" s="19" t="s">
+      <c r="K35" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="19" t="s">
+      <c r="B36" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="F36" s="18">
-        <v>-46.1</v>
-      </c>
-      <c r="G36" s="18">
-        <v>-48.13</v>
-      </c>
-      <c r="H36" s="18">
+      <c r="F36" s="19">
+        <v>-46.09999999999999</v>
+      </c>
+      <c r="G36" s="19">
+        <v>-48.12999999999999</v>
+      </c>
+      <c r="H36" s="19">
         <v>0.12</v>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="19">
         <v>2.03</v>
       </c>
       <c r="J36" s="8">
         <v>17.4</v>
       </c>
-      <c r="K36" s="19" t="s">
+      <c r="K36" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="19" t="s">
+      <c r="B37" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="18">
-        <v>-48.13</v>
-      </c>
-      <c r="G37" s="18">
-        <v>-50.11</v>
-      </c>
-      <c r="H37" s="18">
+      <c r="F37" s="19">
+        <v>-48.12999999999999</v>
+      </c>
+      <c r="G37" s="19">
+        <v>-50.109999999999985</v>
+      </c>
+      <c r="H37" s="19">
         <v>0.18</v>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="19">
         <v>1.98</v>
       </c>
       <c r="J37" s="8">
         <v>10.8</v>
       </c>
-      <c r="K37" s="19" t="s">
+      <c r="K37" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="19" t="s">
+      <c r="B38" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="18">
-        <v>-50.11</v>
-      </c>
-      <c r="G38" s="18">
-        <v>-52.07</v>
-      </c>
-      <c r="H38" s="18">
+      <c r="F38" s="19">
+        <v>-50.109999999999985</v>
+      </c>
+      <c r="G38" s="19">
+        <v>-52.069999999999986</v>
+      </c>
+      <c r="H38" s="19">
         <v>0.15</v>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="19">
         <v>1.96</v>
       </c>
       <c r="J38" s="8">
         <v>13.07</v>
       </c>
-      <c r="K38" s="19" t="s">
+      <c r="K38" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="19" t="s">
+      <c r="B39" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="F39" s="18">
-        <v>-52.07</v>
-      </c>
-      <c r="G39" s="18">
-        <v>-54.11</v>
-      </c>
-      <c r="H39" s="18">
+      <c r="F39" s="19">
+        <v>-52.069999999999986</v>
+      </c>
+      <c r="G39" s="19">
+        <v>-54.109999999999985</v>
+      </c>
+      <c r="H39" s="19">
         <v>0.12</v>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="19">
         <v>2.04</v>
       </c>
       <c r="J39" s="8">
         <v>17.49</v>
       </c>
-      <c r="K39" s="19" t="s">
+      <c r="K39" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="19" t="s">
+      <c r="B40" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="F40" s="18">
-        <v>-54.11</v>
-      </c>
-      <c r="G40" s="18">
-        <v>-56.08</v>
-      </c>
-      <c r="H40" s="18">
+      <c r="F40" s="19">
+        <v>-54.109999999999985</v>
+      </c>
+      <c r="G40" s="19">
+        <v>-56.079999999999984</v>
+      </c>
+      <c r="H40" s="19">
         <v>0.18</v>
       </c>
-      <c r="I40" s="18">
+      <c r="I40" s="19">
         <v>1.97</v>
       </c>
       <c r="J40" s="8">
         <v>10.75</v>
       </c>
-      <c r="K40" s="19" t="s">
+      <c r="K40" s="20" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2287,10 +2287,10 @@
         <v>73</v>
       </c>
       <c r="F41" s="22">
-        <v>-56.08</v>
+        <v>-56.079999999999984</v>
       </c>
       <c r="G41" s="22">
-        <v>-58.11</v>
+        <v>-58.109999999999985</v>
       </c>
       <c r="H41" s="22">
         <v>0.18</v>
@@ -2322,10 +2322,10 @@
         <v>74</v>
       </c>
       <c r="F42" s="22">
-        <v>-58.11</v>
+        <v>-58.109999999999985</v>
       </c>
       <c r="G42" s="22">
-        <v>-60.12</v>
+        <v>-60.11999999999998</v>
       </c>
       <c r="H42" s="22">
         <v>0.18</v>
@@ -2357,10 +2357,10 @@
         <v>76</v>
       </c>
       <c r="F43" s="25">
-        <v>-60.12</v>
+        <v>-60.11999999999998</v>
       </c>
       <c r="G43" s="25">
-        <v>-62.08</v>
+        <v>-62.079999999999984</v>
       </c>
       <c r="H43" s="25">
         <v>0.2</v>
@@ -2392,7 +2392,7 @@
         <v>77</v>
       </c>
       <c r="F44" s="25">
-        <v>-62.08</v>
+        <v>-62.079999999999984</v>
       </c>
       <c r="G44" s="25">
         <v>-64.1</v>
@@ -2438,7 +2438,7 @@
       <c r="I45" s="25">
         <v>1.2</v>
       </c>
-      <c r="J45" s="21">
+      <c r="J45" s="12">
         <v>2.88</v>
       </c>
       <c r="K45" s="26" t="s">
@@ -2629,38 +2629,38 @@
         <v>-20.12</v>
       </c>
       <c r="G3" s="9">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="H3" s="9">
         <v>18.01</v>
       </c>
       <c r="I3" s="8">
-        <v>11.14</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>-20.12</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <v>-22.1</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="13">
         <v>0.22</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="13">
         <v>1.98</v>
       </c>
       <c r="I4" s="8">
@@ -2668,28 +2668,28 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <v>2</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="16">
         <v>-22.1</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="16">
         <v>-26.1</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="16">
         <v>0.33</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="16">
         <v>4</v>
       </c>
       <c r="I5" s="8">
@@ -2697,28 +2697,28 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="19" t="s">
+      <c r="B6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <v>15</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <v>-26.1</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="19">
         <v>-56.08</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="19">
         <v>3.82</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="19">
         <v>29.98</v>
       </c>
       <c r="I6" s="8">
@@ -2803,13 +2803,13 @@
         <v>-65.3</v>
       </c>
       <c r="G9" s="30">
-        <v>8</v>
+        <v>8.37</v>
       </c>
       <c r="H9" s="30">
         <v>69.4</v>
       </c>
       <c r="I9" s="30">
-        <v>8.68</v>
+        <v>8.29</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/f51fae94-b61d-4049-b538-df269cc1ebda_Khách_sạn_Grand_Hyatt_TN_B3_B2_88_D1200_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/f51fae94-b61d-4049-b538-df269cc1ebda_Khách_sạn_Grand_Hyatt_TN_B3_B2_88_D1200_19-03-2026.xlsx
@@ -441,11 +441,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
@@ -457,6 +452,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -597,35 +597,35 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>11</v>
@@ -1584,7 +1584,7 @@
         <v>43</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F21" s="9">
         <v>-16.09</v>
@@ -1593,13 +1593,13 @@
         <v>-18.1</v>
       </c>
       <c r="H21" s="9">
-        <v>0.5</v>
+        <v>0.13</v>
       </c>
       <c r="I21" s="9">
         <v>2.01</v>
       </c>
-      <c r="J21" s="12">
-        <v>4.02</v>
+      <c r="J21" s="8">
+        <v>15.08</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>30</v>
@@ -1641,632 +1641,632 @@
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="12">
         <v>-20.12</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="12">
         <v>-22.1</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="12">
         <v>0.22</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="12">
         <v>1.98</v>
       </c>
       <c r="J23" s="8">
         <v>9.14</v>
       </c>
-      <c r="K23" s="14" t="s">
+      <c r="K23" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="17" t="s">
+      <c r="B24" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="15">
         <v>-22.1</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="15">
         <v>-24.12</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="15">
         <v>0.2</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="15">
         <v>2.02</v>
       </c>
       <c r="J24" s="8">
         <v>10.1</v>
       </c>
-      <c r="K24" s="17" t="s">
+      <c r="K24" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="17" t="s">
+      <c r="B25" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="15">
         <v>-24.12</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="15">
         <v>-26.1</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="15">
         <v>0.13</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="15">
         <v>1.98</v>
       </c>
       <c r="J25" s="8">
         <v>14.85</v>
       </c>
-      <c r="K25" s="17" t="s">
+      <c r="K25" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="20" t="s">
+      <c r="B26" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="E26" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="18">
         <v>-26.1</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="18">
         <v>-28.11</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="18">
         <v>0.33</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="18">
         <v>2.01</v>
       </c>
       <c r="J26" s="8">
         <v>6.03</v>
       </c>
-      <c r="K26" s="20" t="s">
+      <c r="K26" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="20" t="s">
+      <c r="B27" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="18">
         <v>-28.11</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="18">
         <v>-30.13</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="18">
         <v>0.5</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="18">
         <v>2.02</v>
       </c>
-      <c r="J27" s="12">
+      <c r="J27" s="21">
         <v>4.04</v>
       </c>
-      <c r="K27" s="20" t="s">
+      <c r="K27" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="20" t="s">
+      <c r="B28" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="18">
         <v>-30.13</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="18">
         <v>-32.1</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="18">
         <v>0.33</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="18">
         <v>1.97</v>
       </c>
       <c r="J28" s="8">
         <v>5.91</v>
       </c>
-      <c r="K28" s="20" t="s">
+      <c r="K28" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="20" t="s">
+      <c r="B29" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="18">
         <v>-32.1</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="18">
         <v>-34.12</v>
       </c>
-      <c r="H29" s="19">
+      <c r="H29" s="18">
         <v>0.42</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="18">
         <v>2.02</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="21">
         <v>4.85</v>
       </c>
-      <c r="K29" s="20" t="s">
+      <c r="K29" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="20" t="s">
+      <c r="B30" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="18">
         <v>-34.12</v>
       </c>
-      <c r="G30" s="19">
-        <v>-36.10999999999999</v>
-      </c>
-      <c r="H30" s="19">
+      <c r="G30" s="18">
+        <v>-36.11</v>
+      </c>
+      <c r="H30" s="18">
         <v>0.37</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="18">
         <v>1.99</v>
       </c>
       <c r="J30" s="8">
         <v>5.43</v>
       </c>
-      <c r="K30" s="20" t="s">
+      <c r="K30" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="20" t="s">
+      <c r="B31" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="19">
-        <v>-36.10999999999999</v>
-      </c>
-      <c r="G31" s="19">
-        <v>-38.12999999999999</v>
-      </c>
-      <c r="H31" s="19">
+      <c r="F31" s="18">
+        <v>-36.11</v>
+      </c>
+      <c r="G31" s="18">
+        <v>-38.13</v>
+      </c>
+      <c r="H31" s="18">
         <v>0.3</v>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="18">
         <v>2.02</v>
       </c>
       <c r="J31" s="8">
         <v>6.73</v>
       </c>
-      <c r="K31" s="20" t="s">
+      <c r="K31" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="20" t="s">
+      <c r="B32" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F32" s="19">
-        <v>-38.12999999999999</v>
-      </c>
-      <c r="G32" s="19">
-        <v>-40.08999999999999</v>
-      </c>
-      <c r="H32" s="19">
+      <c r="F32" s="18">
+        <v>-38.13</v>
+      </c>
+      <c r="G32" s="18">
+        <v>-40.09</v>
+      </c>
+      <c r="H32" s="18">
         <v>0.33</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="18">
         <v>1.96</v>
       </c>
       <c r="J32" s="8">
         <v>5.88</v>
       </c>
-      <c r="K32" s="20" t="s">
+      <c r="K32" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="20" t="s">
+      <c r="B33" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="19">
-        <v>-40.08999999999999</v>
-      </c>
-      <c r="G33" s="19">
-        <v>-42.09999999999999</v>
-      </c>
-      <c r="H33" s="19">
+      <c r="F33" s="18">
+        <v>-40.09</v>
+      </c>
+      <c r="G33" s="18">
+        <v>-42.1</v>
+      </c>
+      <c r="H33" s="18">
         <v>0.17</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="18">
         <v>2.01</v>
       </c>
       <c r="J33" s="8">
         <v>12.06</v>
       </c>
-      <c r="K33" s="20" t="s">
+      <c r="K33" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="20" t="s">
+      <c r="B34" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="21" t="s">
+      <c r="E34" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="19">
-        <v>-42.09999999999999</v>
-      </c>
-      <c r="G34" s="19">
-        <v>-44.11999999999998</v>
-      </c>
-      <c r="H34" s="19">
+      <c r="F34" s="18">
+        <v>-42.1</v>
+      </c>
+      <c r="G34" s="18">
+        <v>-44.12</v>
+      </c>
+      <c r="H34" s="18">
         <v>0.13</v>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="18">
         <v>2.02</v>
       </c>
       <c r="J34" s="8">
         <v>15.15</v>
       </c>
-      <c r="K34" s="20" t="s">
+      <c r="K34" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="20" t="s">
+      <c r="B35" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="21" t="s">
+      <c r="E35" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F35" s="19">
-        <v>-44.11999999999998</v>
-      </c>
-      <c r="G35" s="19">
-        <v>-46.09999999999999</v>
-      </c>
-      <c r="H35" s="19">
+      <c r="F35" s="18">
+        <v>-44.12</v>
+      </c>
+      <c r="G35" s="18">
+        <v>-46.1</v>
+      </c>
+      <c r="H35" s="18">
         <v>0.18</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="18">
         <v>1.98</v>
       </c>
       <c r="J35" s="8">
         <v>10.8</v>
       </c>
-      <c r="K35" s="20" t="s">
+      <c r="K35" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="20" t="s">
+      <c r="B36" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F36" s="19">
-        <v>-46.09999999999999</v>
-      </c>
-      <c r="G36" s="19">
-        <v>-48.12999999999999</v>
-      </c>
-      <c r="H36" s="19">
+      <c r="F36" s="18">
+        <v>-46.1</v>
+      </c>
+      <c r="G36" s="18">
+        <v>-48.13</v>
+      </c>
+      <c r="H36" s="18">
         <v>0.12</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="18">
         <v>2.03</v>
       </c>
       <c r="J36" s="8">
         <v>17.4</v>
       </c>
-      <c r="K36" s="20" t="s">
+      <c r="K36" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="20" t="s">
+      <c r="B37" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="19">
-        <v>-48.12999999999999</v>
-      </c>
-      <c r="G37" s="19">
-        <v>-50.109999999999985</v>
-      </c>
-      <c r="H37" s="19">
+      <c r="F37" s="18">
+        <v>-48.13</v>
+      </c>
+      <c r="G37" s="18">
+        <v>-50.11</v>
+      </c>
+      <c r="H37" s="18">
         <v>0.18</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="18">
         <v>1.98</v>
       </c>
       <c r="J37" s="8">
         <v>10.8</v>
       </c>
-      <c r="K37" s="20" t="s">
+      <c r="K37" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="20" t="s">
+      <c r="B38" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="19">
-        <v>-50.109999999999985</v>
-      </c>
-      <c r="G38" s="19">
-        <v>-52.069999999999986</v>
-      </c>
-      <c r="H38" s="19">
+      <c r="F38" s="18">
+        <v>-50.11</v>
+      </c>
+      <c r="G38" s="18">
+        <v>-52.07</v>
+      </c>
+      <c r="H38" s="18">
         <v>0.15</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="18">
         <v>1.96</v>
       </c>
       <c r="J38" s="8">
         <v>13.07</v>
       </c>
-      <c r="K38" s="20" t="s">
+      <c r="K38" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="20" t="s">
+      <c r="B39" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="D39" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="E39" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F39" s="19">
-        <v>-52.069999999999986</v>
-      </c>
-      <c r="G39" s="19">
-        <v>-54.109999999999985</v>
-      </c>
-      <c r="H39" s="19">
+      <c r="F39" s="18">
+        <v>-52.07</v>
+      </c>
+      <c r="G39" s="18">
+        <v>-54.11</v>
+      </c>
+      <c r="H39" s="18">
         <v>0.12</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="18">
         <v>2.04</v>
       </c>
       <c r="J39" s="8">
         <v>17.49</v>
       </c>
-      <c r="K39" s="20" t="s">
+      <c r="K39" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="20" t="s">
+      <c r="B40" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="D40" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E40" s="21" t="s">
+      <c r="E40" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F40" s="19">
-        <v>-54.109999999999985</v>
-      </c>
-      <c r="G40" s="19">
-        <v>-56.079999999999984</v>
-      </c>
-      <c r="H40" s="19">
+      <c r="F40" s="18">
+        <v>-54.11</v>
+      </c>
+      <c r="G40" s="18">
+        <v>-56.08</v>
+      </c>
+      <c r="H40" s="18">
         <v>0.18</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="18">
         <v>1.97</v>
       </c>
       <c r="J40" s="8">
         <v>10.75</v>
       </c>
-      <c r="K40" s="20" t="s">
+      <c r="K40" s="19" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2287,10 +2287,10 @@
         <v>73</v>
       </c>
       <c r="F41" s="22">
-        <v>-56.079999999999984</v>
+        <v>-56.08</v>
       </c>
       <c r="G41" s="22">
-        <v>-58.109999999999985</v>
+        <v>-58.11</v>
       </c>
       <c r="H41" s="22">
         <v>0.18</v>
@@ -2322,10 +2322,10 @@
         <v>74</v>
       </c>
       <c r="F42" s="22">
-        <v>-58.109999999999985</v>
+        <v>-58.11</v>
       </c>
       <c r="G42" s="22">
-        <v>-60.11999999999998</v>
+        <v>-60.12</v>
       </c>
       <c r="H42" s="22">
         <v>0.18</v>
@@ -2357,10 +2357,10 @@
         <v>76</v>
       </c>
       <c r="F43" s="25">
-        <v>-60.11999999999998</v>
+        <v>-60.12</v>
       </c>
       <c r="G43" s="25">
-        <v>-62.079999999999984</v>
+        <v>-62.08</v>
       </c>
       <c r="H43" s="25">
         <v>0.2</v>
@@ -2392,7 +2392,7 @@
         <v>77</v>
       </c>
       <c r="F44" s="25">
-        <v>-62.079999999999984</v>
+        <v>-62.08</v>
       </c>
       <c r="G44" s="25">
         <v>-64.1</v>
@@ -2438,7 +2438,7 @@
       <c r="I45" s="25">
         <v>1.2</v>
       </c>
-      <c r="J45" s="12">
+      <c r="J45" s="21">
         <v>2.88</v>
       </c>
       <c r="K45" s="26" t="s">
@@ -2629,38 +2629,38 @@
         <v>-20.12</v>
       </c>
       <c r="G3" s="9">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="H3" s="9">
         <v>18.01</v>
       </c>
       <c r="I3" s="8">
-        <v>9.08</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-20.12</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-22.1</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>0.22</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>1.98</v>
       </c>
       <c r="I4" s="8">
@@ -2668,28 +2668,28 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="B5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>2</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-22.1</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>-26.1</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>0.33</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>4</v>
       </c>
       <c r="I5" s="8">
@@ -2697,28 +2697,28 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="20" t="s">
+      <c r="B6" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>15</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>-26.1</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>-56.08</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>3.82</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>29.98</v>
       </c>
       <c r="I6" s="8">
@@ -2803,13 +2803,13 @@
         <v>-65.3</v>
       </c>
       <c r="G9" s="30">
-        <v>8.37</v>
+        <v>8</v>
       </c>
       <c r="H9" s="30">
         <v>69.4</v>
       </c>
       <c r="I9" s="30">
-        <v>8.29</v>
+        <v>8.68</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/f51fae94-b61d-4049-b538-df269cc1ebda_Khách_sạn_Grand_Hyatt_TN_B3_B2_88_D1200_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/f51fae94-b61d-4049-b538-df269cc1ebda_Khách_sạn_Grand_Hyatt_TN_B3_B2_88_D1200_19-03-2026.xlsx
@@ -139,9 +139,6 @@
 18/03/2026</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t xml:space="preserve">08:20
 18/03/2026</t>
   </si>
@@ -174,6 +171,9 @@
   <si>
     <t xml:space="preserve">09:20
 18/03/2026</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>Sét - Sét pha màu xám xanh, xám ghi, xám vàng, nâu đỏ, trạng thái dẻo cứng đến nửa cứng</t>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>11</v>
@@ -1444,7 +1444,7 @@
         <v>38</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17" s="9">
         <v>-8.1</v>
@@ -1476,10 +1476,10 @@
         <v>34</v>
       </c>
       <c r="D18" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="F18" s="9">
         <v>-10.13</v>
@@ -1511,10 +1511,10 @@
         <v>34</v>
       </c>
       <c r="D19" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="F19" s="9">
         <v>-12.1</v>
@@ -1546,10 +1546,10 @@
         <v>34</v>
       </c>
       <c r="D20" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>42</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>43</v>
       </c>
       <c r="F20" s="9">
         <v>-14.12</v>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>11</v>
@@ -1581,10 +1581,10 @@
         <v>34</v>
       </c>
       <c r="D21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>44</v>
       </c>
       <c r="F21" s="9">
         <v>-16.09</v>
@@ -1616,10 +1616,10 @@
         <v>34</v>
       </c>
       <c r="D22" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>45</v>
       </c>
       <c r="F22" s="9">
         <v>-18.1</v>
@@ -1642,19 +1642,19 @@
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="14" t="s">
         <v>47</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>48</v>
       </c>
       <c r="F23" s="12">
         <v>-20.12</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>11</v>
@@ -1686,7 +1686,7 @@
         <v>49</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>50</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>11</v>
@@ -2646,7 +2646,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>

--- a/SGC-CKN/Excel/f51fae94-b61d-4049-b538-df269cc1ebda_Khách_sạn_Grand_Hyatt_TN_B3_B2_88_D1200_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/f51fae94-b61d-4049-b538-df269cc1ebda_Khách_sạn_Grand_Hyatt_TN_B3_B2_88_D1200_19-03-2026.xlsx
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi</t>
+    <t>Khách sạn GrandHyatt</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TN-B3-B2.88</t>
+    <t>B2.88</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -120,7 +120,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét pha - cát pha màu xám xanh, xám đen, trạng thái dẻo chảy đến chảy</t>
+    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo chảy đến chảy</t>
   </si>
   <si>
     <t xml:space="preserve">07:30
@@ -166,7 +166,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét pha màu xám xanh, xám đen, trạng thái dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">09:20
@@ -176,7 +176,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét - Sét pha màu xám xanh, xám ghi, xám vàng, nâu đỏ, trạng thái dẻo cứng đến nửa cứng</t>
+    <t>Sét pha, xám xanh, xám đen, xám ghi, xám vàng, nâu đỏ, TT dẻo cứng đến nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">09:32
@@ -264,7 +264,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sét pha màu xám xanh, xám đen, trạng thái nửa cứng đến cứng</t>
+    <t>Sét pha, xám xanh, xám đen, trạng thái nửa cứng đến cứng</t>
   </si>
   <si>
     <t xml:space="preserve">08:25
